--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87291891</v>
+        <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>97564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,34 +939,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Stenklammen, Stenklammen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419867</v>
+        <v>420253</v>
       </c>
       <c r="R4" t="n">
-        <v>6678920</v>
+        <v>6679337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +998,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fläckvis på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,27 +1033,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87291891</t>
+          <t>https://artportalen.se/Sighting/136381781</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87291895</v>
+        <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>97564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,34 +1061,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Stenklammen, Stenklammen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420146</v>
+        <v>420293</v>
       </c>
       <c r="R5" t="n">
-        <v>6679076</v>
+        <v>6679353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1115,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ganska rikligt på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1150,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87291895</t>
+          <t>https://artportalen.se/Sighting/136382782</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87293326</v>
+        <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>97564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,34 +1178,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Stenklammen, Stenklammen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420010</v>
+        <v>420290</v>
       </c>
       <c r="R6" t="n">
-        <v>6679214</v>
+        <v>6679273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,12 +1232,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,27 +1267,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87293326</t>
+          <t>https://artportalen.se/Sighting/136383003</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87293335</v>
+        <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>97564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,34 +1295,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Stenklammen, Stenklammen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420315</v>
+        <v>420280</v>
       </c>
       <c r="R7" t="n">
-        <v>6679507</v>
+        <v>6679280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,12 +1349,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,62 +1384,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87293335</t>
+          <t>https://artportalen.se/Sighting/136383126</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87291882</v>
+        <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>97564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419873</v>
+        <v>420123</v>
       </c>
       <c r="R8" t="n">
-        <v>6678924</v>
+        <v>6679072</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,12 +1466,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,62 +1501,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87291882</t>
+          <t>https://artportalen.se/Sighting/136385902</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87291885</v>
+        <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>97564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420062</v>
+        <v>420101</v>
       </c>
       <c r="R9" t="n">
-        <v>6679202</v>
+        <v>6679002</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,12 +1583,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,62 +1618,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87291885</t>
+          <t>https://artportalen.se/Sighting/136386118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87293329</v>
+        <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>97564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420082</v>
+        <v>419904</v>
       </c>
       <c r="R10" t="n">
-        <v>6679152</v>
+        <v>6678829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,12 +1700,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,74 +1730,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87293329</t>
+          <t>https://artportalen.se/Sighting/136387141</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131928</v>
+        <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>97564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenklammen, Stenklammen, Vrm</t>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420309</v>
+        <v>419842</v>
       </c>
       <c r="R11" t="n">
-        <v>6679518</v>
+        <v>6678828</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,22 +1812,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,56 +1838,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sofia Österdahl</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Österdahl</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129131928</t>
+          <t>https://artportalen.se/Sighting/136387286</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87293325</v>
+        <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>97564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,34 +1870,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Östra Tönnet, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420228</v>
+        <v>420243</v>
       </c>
       <c r="R12" t="n">
-        <v>6679403</v>
+        <v>6679235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,12 +1936,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,33 +1960,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Petter Brorson Edh</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Petter Brorson Edh</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87293325</t>
+          <t>https://artportalen.se/Sighting/136392867</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87291881</v>
+        <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>92037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,34 +1995,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Stenklammen, Stenklammen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>420063</v>
+        <v>420391</v>
       </c>
       <c r="R13" t="n">
-        <v>6679215</v>
+        <v>6679524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,12 +2063,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På grov tallåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,27 +2098,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87291881</t>
+          <t>https://artportalen.se/Sighting/136378941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87293332</v>
+        <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>92037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,34 +2126,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ekshärad, Vrm</t>
+          <t>Stenklammen, Stenklammen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420005</v>
+        <v>420353</v>
       </c>
       <c r="R14" t="n">
-        <v>6679216</v>
+        <v>6679488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,12 +2183,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,27 +2213,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Jens Johansen, Olle Kvarnbäck, Petter Brorson Edh, Maja Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87293332</t>
+          <t>https://artportalen.se/Sighting/136387804</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87293336</v>
+        <v>87291891</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,21 +2241,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420315</v>
+        <v>419867</v>
       </c>
       <c r="R15" t="n">
-        <v>6679507</v>
+        <v>6678920</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,18 +2315,3424 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/87291891</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>87291895</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>420146</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6679076</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87291895</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>87293326</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>353</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>420010</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6679214</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87293326</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>87293335</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>353</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>420315</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6679507</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87293335</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136380752</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79126</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>353</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>420339</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6679428</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På brandstubbe av tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380752</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>87291882</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>419873</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6678924</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87291882</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>87291885</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>420062</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6679202</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87291885</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>87293329</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>420082</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6679152</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87293329</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129131928</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>420309</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6679518</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sofia Österdahl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sofia Österdahl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131928</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>87293325</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>420228</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6679403</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87293325</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136377751</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>420391</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6679524</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På kolad brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136377751</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136380847</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>420339</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6679428</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380847</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136381090</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>420305</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6679424</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136381090</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136381593</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>420293</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6679353</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136381593</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136383972</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>420213</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6679149</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136383972</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136385942</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>420107</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6679002</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136385942</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>87291881</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>420063</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6679215</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87291881</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>87293332</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>420005</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6679216</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87293332</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>87293336</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ekshärad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>420315</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6679507</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/87293336</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136381157</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>420305</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6679424</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136381157</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136382055</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>420253</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6679337</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136382055</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136383951</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>420213</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6679149</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På silvervedstubbe</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136383951</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136387470</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>419848</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6679104</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136387470</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136384553</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>420213</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6679149</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hackmärken i tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136384553</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136377437</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58149</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>420391</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6679524</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136377437</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136383352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>420280</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6679280</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136383352</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136382388</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99244</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>420230</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6679304</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136382388</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136381242</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>420305</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6679424</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136381242</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136382105</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>420253</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6679337</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136382105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136382144</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stenklammen, Stenklammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>420230</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6679319</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136382144</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136385918</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tönnetsrostbäcken, Tönnetsrostbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>420123</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6679072</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136385918</t>
         </is>
       </c>
     </row>
@@ -2210,6 +5752,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136380752</v>
       </c>
       <c r="B19" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136377751</v>
       </c>
       <c r="B25" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>136380847</v>
       </c>
       <c r="B26" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136381090</v>
       </c>
       <c r="B27" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136381593</v>
       </c>
       <c r="B28" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136383972</v>
       </c>
       <c r="B29" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136385942</v>
       </c>
       <c r="B30" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136381157</v>
       </c>
       <c r="B34" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>136382055</v>
       </c>
       <c r="B35" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>136383951</v>
       </c>
       <c r="B36" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>136387470</v>
       </c>
       <c r="B37" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>136384553</v>
       </c>
       <c r="B38" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>136377437</v>
       </c>
       <c r="B39" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136381242</v>
       </c>
       <c r="B42" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136382105</v>
       </c>
       <c r="B43" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>136382144</v>
       </c>
       <c r="B44" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>136385918</v>
       </c>
       <c r="B45" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136380752</v>
       </c>
       <c r="B19" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136377751</v>
       </c>
       <c r="B25" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>136380847</v>
       </c>
       <c r="B26" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136381090</v>
       </c>
       <c r="B27" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136381593</v>
       </c>
       <c r="B28" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136383972</v>
       </c>
       <c r="B29" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136385942</v>
       </c>
       <c r="B30" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136381157</v>
       </c>
       <c r="B34" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>136382055</v>
       </c>
       <c r="B35" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>136383951</v>
       </c>
       <c r="B36" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>136387470</v>
       </c>
       <c r="B37" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136381242</v>
       </c>
       <c r="B42" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136382105</v>
       </c>
       <c r="B43" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>136382144</v>
       </c>
       <c r="B44" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>136385918</v>
       </c>
       <c r="B45" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
